--- a/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_iteration_1.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_iteration_1.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 もし時間があったら、(   )。</t>
+          <t>: もんだい1 もし時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 しけんが終わったら、(   )。</t>
+          <t>: もんだい1 しけんが終わったら、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 家に帰ったら、(   )。</t>
+          <t>: もんだい1 家に帰ったら、(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 本を読んだら、(   )。</t>
+          <t>: もんだい1 本を読んだら、(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 旅行が終わったら、(   )。</t>
+          <t>: もんだい1 旅行が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 朝ごはんを食べたら、(   )。</t>
+          <t>: もんだい1 朝ごはんを食べたら、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 電話が来たら、(   )。</t>
+          <t>: もんだい1 電話が来たら、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 雨が降ったら、(   )。</t>
+          <t>: もんだい1 雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 お金があったら、(   )。</t>
+          <t>: もんだい1 お金があったら、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. 新しいカメラを買います 2. 車を修理します 3. 家を掃除します 4. 旅行に行きます</t>
+          <t>1. 旅行に行きます 2. 新しいカメラを買います 3. 車を修理します 4. 家を掃除します</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨が ふったら サッカーの試合は 中止 (   ) なる。</t>
+          <t>: もんだい2 雨が降ったら、サッカーの試合は中止(   )なります。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -702,12 +702,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 このボタンを 押したら、ドアが (   )。</t>
+          <t>: もんだい2 このボタンを 押したら、ドアが (   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -726,12 +726,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
+          <t>: もんだい2 友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -750,12 +750,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 かぜを ひいたら、早く 寝る (   ) いいですよ。</t>
+          <t>: もんだい2 風邪をひいたら、早く寝たほうがいいですよ。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -774,12 +774,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
+          <t>: もんだい2 お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 駅に 着いたら 電話 (   ) ください。</t>
+          <t>: もんだい2 駅に 着いたら 電話 (   ) ください。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 もし、彼に 会えたら、この 手紙を (   )。</t>
+          <t>: もんだい2 もし、彼に 会えたら、この 手紙を (   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -846,12 +846,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 宿題が 終わったら、遊びに (   ) 行きましょう。</t>
+          <t>: もんだい2 宿題が 終わったら、遊びに (   ) 行きましょう。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 天気が よかったら、明日 (   ) 行きます。</t>
+          <t>: もんだい2 天気がよかったら、明日(   )に行きます。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -894,12 +894,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あったら、映画を (   ) 見に行きます。</t>
+          <t>: もんだい2 時間があったら、映画を(   )見に行きます。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -918,12 +918,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降ったら、(   )。</t>
+          <t>: もんだい3 雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -942,17 +942,17 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 宿題が終わったら、(   )。</t>
+          <t>: もんだい3 宿題が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>1. あそびます 2. あそんで 3. あそばない 4. あそびません</t>
+          <t>1. あそびます 2. あそんでいます 3. あそばない 4. あそびません</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -966,17 +966,17 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金を持っていたら、(   )。</t>
+          <t>: もんだい3 お金を持っていたら、(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>1. 買います 2. 買いません 3. 買う 4. 買わない</t>
+          <t>1. 買います 2. 買いません 3. 買うでしょう 4. 買わないでしょう</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -990,17 +990,17 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があったら、(   )。</t>
+          <t>: もんだい3 時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>1. でかけます 2. でかけない 3. でかけません 4. でかける</t>
+          <t>1. でかけます 2. でかけません 3. でかけよう 4. でかけるでしょう</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1014,17 +1014,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 図書館に行ったら、(   )。</t>
+          <t>: もんだい3 図書館に行ったら、(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>1. 本を借ります 2. 本を読む 3. 本を探す 4. 本を返す</t>
+          <t>1. 本を借ります 2. 本を読みます 3. 本を探します 4. 本を返します</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1038,17 +1038,17 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達が来たら、(   )。</t>
+          <t>: もんだい3 友達が来たら、(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーをします 2. 話をします 3. 一緒に遊びます 4. お茶を飲みます</t>
+          <t>1. お茶を飲みます 2. パーティーをします 3. 話をします 4. 一緒に遊びます</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1062,17 +1062,17 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 電車が遅れたら、(   )。</t>
+          <t>: もんだい3 電車が遅れたら、(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>1. ちこくします 2. ちこくする 3. ちこくしない 4. ちこくしません</t>
+          <t>1. 遅れます 2. 遅れるかもしれません 3. 遅れないです 4. 遅れません</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 映画が終わったら、(   )。</t>
+          <t>: もんだい3 映画が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1110,22 +1110,22 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 もし雨が降ったら、(   )。</t>
+          <t>: もんだい3 もし雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>1. 傘をさします 2. 雨宿りします 3. 帰ります 4. 走ります</t>
+          <t>1. 雨宿りします 2. 傘をさします 3. 帰ります 4. 走ります</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr"/>
@@ -1134,17 +1134,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 冬になったら、(   )。</t>
+          <t>: もんだい3 冬になったら、(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. さむくなります 2. コートを着ます 3. スキーをします 4. 暖房を使います</t>
+          <t>1. コートを着ます 2. さむくなります 3. スキーをします 4. 暖房を使います</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1158,12 +1158,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が たくさん あったら、 新しい車を (   ).</t>
+          <t>: もんだい4 もし お金が たくさん あったら、 新しい車を (   ).</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1182,22 +1182,22 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降ったら、 試合は (   ).</t>
+          <t>: もんだい4 もし雨が降ったら、試合は(   )。</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>1. 中止する 2. 中止したい 3. 中止するかもしれない 4. 中止した</t>
+          <t>1. 中止になります 2. 中止したいです 3. 中止するかもしれません 4. 中止した</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr"/>
@@ -1206,12 +1206,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
+          <t>: もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1230,22 +1230,22 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 暇だったら、 手伝いに (   ).</t>
+          <t>: もんだい4 もし暇だったら、手伝いに(   )。</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>1. 行くことにする 2. 行くかもしれない 3. 行くつもり 4. 行きたがる</t>
+          <t>1. 行きます 2. 行きたいです 3. 行くつもりです 4. 行きたがります</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr"/>
@@ -1254,22 +1254,22 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
+          <t>: もんだい4 もし時間があったら、新しいレストランで食事を(   )。</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1. することにした 2. したい 3. したがっている 4. するらしい</t>
+          <t>1. します 2. したいです 3. したがっています 4. するらしいです</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
+          <t>: もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1302,12 +1302,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
+          <t>: もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1326,12 +1326,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
+          <t>: もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1350,22 +1350,22 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 間違えたら、 すぐに 先生に (   ).</t>
+          <t>: もんだい4 もし間違えたら、すぐに先生に(   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>1. 聞くことにした 2. 聞きたがる 3. 聞くつもりだ 4. 聞いた</t>
+          <t>1. 聞きます 2. 聞きたいです 3. 聞くつもりです 4. 聞いた</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr"/>
@@ -1374,17 +1374,17 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
+          <t>: もんだい4 もし彼女が行かないなら、わたしも行かない(   )。</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. ことにした 2. かもしれない 3. つもりだ 4. そうだ</t>
+          <t>1. です 2. かもしれません 3. つもりです 4. そうです</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降ったら、試合は (   )。</t>
+          <t>: もんだい5 雨が降ったら、試合は (   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1422,17 +1422,17 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 もし彼が来たら、私はすぐに (   )。</t>
+          <t>: もんだい5 もし彼が来たら、私はすぐに(   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>1. 行きます 2. 準備します 3. 話します 4. 迎えます</t>
+          <t>1. 迎えます 2. 行きます 3. 準備します 4. 話します</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -1446,17 +1446,17 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この仕事が終わったら、(   )。</t>
+          <t>: もんだい5 この仕事が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>1. 帰ります 2. 休みます 3. 昼ご飯を食べます 4. 散歩します</t>
+          <t>1. 休みます 2. 帰ります 3. 昼ご飯を食べます 4. 散歩します</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -1470,12 +1470,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 時間があったら、映画を (   )。</t>
+          <t>: もんだい5 時間があったら、映画を(   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1494,12 +1494,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼女が手伝ったら、もっと早く (   )。</t>
+          <t>: もんだい5 彼女が手伝ったら、もっと早く(   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この本を読んだら、次に何を (   )。</t>
+          <t>: もんだい5 この本を読んだら、次に何を(   )。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1542,17 +1542,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 友達が来たら、ゲームを一緒に (   )。</t>
+          <t>: もんだい5 友達が来たら、ゲームを一緒に(   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>1. します 2. 食べます 3. 聞きます 4. 見ます</t>
+          <t>1. します 2. 見ます 3. 聞きます 4. 食べます</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -1566,17 +1566,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 電車が遅れたら、授業に (   )。</t>
+          <t>: もんだい5 電車が遅れたら、授業に(   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>1. 間に合いません 2. 遅れます 3. 行きません 4. 出ません</t>
+          <t>1. 遅れます 2. 間に合いません 3. 行きません 4. 出ません</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1590,17 +1590,17 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 もしお金がたくさんあったら、旅行に (   )。</t>
+          <t>: もんだい5 もしお金がたくさんあったら、旅行に(   )。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたい 2. 買いたい 3. 住みたい 4. 食べたい</t>
+          <t>1. 行きたいです 2. 買いたいです 3. 住みたいです 4. 食べたいです</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が答えたら、みんなが (   )。</t>
+          <t>: もんだい5 彼が答えたら、みんなが(   )。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
+          <t>: もんだい6 A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1662,17 +1662,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
+          <t>: もんだい6 A:「もし道に迷ったら、どうしますか。」 B:「すぐにアプリで(   )。」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>1. 調べます 2. 見つけます 3. 探します 4. 聞きます</t>
+          <t>1. 探します 2. 調べます 3. 見つけます 4. 聞きます</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -1686,12 +1686,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
+          <t>: もんだい6 A:「テストが終わったら、何をしますか。」 B:「終わったら、友達とカフェに(   )。」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1710,12 +1710,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
+          <t>: もんだい6 A:「明日暇だったら、何をしますか。」 B:「暇だったら、家でゆっくり(   )。」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
+          <t>: もんだい6 A:「もし、時間があったら、手伝ってもらえますか。」 B:「時間があったら、もちろん(   )。」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1758,12 +1758,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
+          <t>: もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。」 B:「予定がなかったら、海に(   )。」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1782,12 +1782,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
+          <t>: もんだい6 A:「バスが遅れたら、どうしますか。」 B:「遅れたら、タクシーを(   )。」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr"/>
@@ -1806,12 +1806,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
+          <t>: もんだい6 A:「もし、財布を忘れたら、どうしますか。」 B:「忘れたら、友達に(   )。」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1830,12 +1830,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
+          <t>: もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。」 B:「雨が降ったら、ピクニックは(   )。」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1854,12 +1854,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
+          <t>: もんだい6 A:「試験に合格したら、何をしますか。」 B:「合格したら、家族と(   )。」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 雨が 降ったら (   )。</t>
+          <t>: もんだい7 もし雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1902,12 +1902,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 テストが 終わったら (   )。</t>
+          <t>: もんだい7 テストが終わったら、(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1926,12 +1926,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし お金が あったら、(   )。</t>
+          <t>: もんだい7 もしお金ががあったら、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 時間が あったら (   )。</t>
+          <t>: もんだい7 時間ががあったら、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1974,12 +1974,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 彼が 来たら、(   )。</t>
+          <t>: もんだい7 もし彼が来たら、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -1998,12 +1998,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 パーティーが 終わったら (   )。</t>
+          <t>: もんだい7 パーティーが終わったら、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2022,17 +2022,17 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼女が 行くと 言ったら、(   )。</t>
+          <t>: もんだい7 彼女が行くと言ったら、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>1. 行かないことにする 2. 行くことにした 3. 行こうと思った 4. 行くことができる</t>
+          <t>1. 行かないことにする 2. 行くことにする 3. 行こうと思った 4. 行くことができる</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
@@ -2046,12 +2046,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 道が わからなかったら、(   )。</t>
+          <t>: もんだい7 もし道がわからなかったら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 天気が よかったら、(   )。</t>
+          <t>: もんだい7 天気がよかったら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2094,12 +2094,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 先生が 来たら、(   )。</t>
+          <t>: もんだい7 先生が来たら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2118,12 +2118,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
+          <t>: もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2142,12 +2142,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
+          <t>: もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2166,12 +2166,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
+          <t>: もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2190,12 +2190,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
+          <t>: もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
+          <t>: もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
+          <t>: もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2262,12 +2262,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
+          <t>: もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2286,12 +2286,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
+          <t>: もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
+          <t>: もんだい8 もし雨が降ったら、(   )家に帰ります。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2334,12 +2334,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
+          <t>: もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
